--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580"/>
+    <workbookView windowWidth="16635" windowHeight="11565"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Name</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Computer Science</t>
   </si>
   <si>
-    <t>Tayson</t>
+    <t>Yousef</t>
   </si>
   <si>
     <t>Business Technology</t>
@@ -65,25 +65,19 @@
     <t>Khairy</t>
   </si>
   <si>
-    <t>0pama</t>
+    <t>Mohamed</t>
   </si>
   <si>
     <t xml:space="preserve">Biotechnology </t>
   </si>
   <si>
-    <t>Fakhr</t>
+    <t>Abdelrahman</t>
   </si>
   <si>
     <t>Physical Therapy</t>
   </si>
   <si>
-    <t>Lord</t>
-  </si>
-  <si>
-    <t>Virus</t>
-  </si>
-  <si>
-    <t>Speed</t>
+    <t>Ahmed</t>
   </si>
   <si>
     <t>Hazem</t>
@@ -98,7 +92,7 @@
     <t>Nutrition Sciences</t>
   </si>
   <si>
-    <t>Felo</t>
+    <t>Felopater</t>
   </si>
   <si>
     <t>Pharmacy</t>
@@ -759,12 +753,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
@@ -1142,10 +1135,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1159,20 +1152,20 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>98</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>92</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>64</v>
       </c>
       <c r="G2">
         <v>90</v>
       </c>
     </row>
-    <row r="3" ht="15.75" spans="1:7">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1182,13 +1175,13 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>76</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>81</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>84</v>
       </c>
       <c r="G3">
@@ -1205,20 +1198,20 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>91</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>87</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>89</v>
       </c>
       <c r="G4">
         <v>89</v>
       </c>
     </row>
-    <row r="5" ht="15.75" spans="1:7">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1228,20 +1221,20 @@
       <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>68</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>74</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>72</v>
       </c>
       <c r="G5">
         <v>72</v>
       </c>
     </row>
-    <row r="6" ht="15.75" spans="1:7">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1251,22 +1244,22 @@
       <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>82</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>78</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6">
         <v>80</v>
       </c>
     </row>
-    <row r="7" ht="15.75" spans="1:7">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>22</v>
@@ -1274,22 +1267,22 @@
       <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>95</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>90</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>96</v>
       </c>
       <c r="G7">
         <v>96</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:7">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>20</v>
@@ -1297,22 +1290,22 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>73</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>69</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>75</v>
       </c>
       <c r="G8">
         <v>75</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="1:7">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>24</v>
@@ -1320,13 +1313,13 @@
       <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>61</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>66</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>70</v>
       </c>
       <c r="G9">
@@ -1335,21 +1328,21 @@
     </row>
     <row r="10" ht="15.75" spans="1:7">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="4">
+        <v>18</v>
+      </c>
+      <c r="D10" s="3">
         <v>87</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>83</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>86</v>
       </c>
       <c r="G10">
@@ -1358,44 +1351,44 @@
     </row>
     <row r="11" ht="15.75" spans="1:7">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="4">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3">
         <v>79</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>85</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>78</v>
       </c>
       <c r="G11">
         <v>90</v>
       </c>
     </row>
-    <row r="12" ht="15.75" spans="1:7">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="4">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3">
         <v>90</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>88</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>92</v>
       </c>
       <c r="G12">
